--- a/04_regulatory-compliance-for-ai-eu-ai-act/exercises/solution/compliance_plan.xlsx
+++ b/04_regulatory-compliance-for-ai-eu-ai-act/exercises/solution/compliance_plan.xlsx
@@ -1109,8 +1109,8 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>"Extend logging to video analysis pipeline; formalize retention policy (minimum 5 years for EU AI Act); add culture fit scoring audit trail"
-Reasoning: 5-year retention meets EU AI Act minimum. Extending logging to video and culture fit enables the auditability required for high-risk systems.</t>
+          <t>"Extend logging to video analysis pipeline; formalize retention policy (statutory floor ≥6 months per Arts. 19(1)/26(6); 5 years retained as internal standard); add culture fit scoring audit trail"
+Reasoning: The EU AI Act log-retention floor is at least six months (Art. 19(1) for providers, Art. 26(6) for deployers); Article 12 governs the logging capability itself, not a retention period. The 5-year period is an internal enterprise standard layered on top, defensible for employment-decision records. Extending logging to video and culture fit enables the auditability required for high-risk systems.</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -2252,17 +2252,17 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>General-Purpose AI models — including those with systemic risk. Added in 2026 EU AI Act refresh.</t>
+          <t>General-Purpose AI models — including those with systemic risk. Introduced by Regulation (EU) 2024/1689; obligations applicable from 2 Aug 2025.</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Foundation-model APIs embedded in customer-facing assistants, chatbots, code copilots, RAG systems.</t>
+          <t>Providers of general-purpose foundation models — e.g. models offered via API that power customer-facing assistants, chatbots, code copilots, RAG systems.</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Transparency to downstream deployers (Art. 53), copyright disclosure, technical documentation; if systemic risk, additional model evaluation + adversarial testing + Art. 55 obligations.</t>
+          <t>Provider obligations — transparency to downstream deployers (Art. 53), copyright disclosure, technical documentation; if systemic risk, additional model evaluation + adversarial testing + Art. 55 obligations.</t>
         </is>
       </c>
     </row>

--- a/04_regulatory-compliance-for-ai-eu-ai-act/exercises/solution/compliance_plan.xlsx
+++ b/04_regulatory-compliance-for-ai-eu-ai-act/exercises/solution/compliance_plan.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,6 +79,14 @@
       <i val="1"/>
       <color rgb="FF7F6000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -158,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -190,6 +198,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1466,6 +1477,22 @@
           <t>"Establish 15-day reporting SLA to national competent authority; integrate incident detection from SP6 IR playbook; assign DPO + Compliance lead as joint owners; complete documentation by Q2 2026 ahead of August 2026 enforcement."</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>"Stand up the Article 73 reporting workflow: 15-day SLA to the national competent authority (10 days where the incident involves a person's death; 2 days for widespread infringement); wire incident detection in from the SP6 IR playbook; define the escalation path and DPO + Compliance joint sign-off; dry-run the process before Aug 2026."
+Reasoning: Article 73 becomes enforceable in August 2026, so the workflow must exist and be rehearsed before then. Reusing the SP6 detection pipeline avoids building a parallel capability, and joint DPO + Compliance sign-off matches the tiered deadlines.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>DPO + Compliance</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2161,17 +2188,17 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Prohibited AI practices.</t>
+          <t>Prohibited AI practices that pose unacceptable risk.</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Social scoring, real-time public biometric surveillance, manipulation of vulnerable persons, predictive policing</t>
+          <t>Social scoring by governments, real-time biometric mass surveillance in public spaces, manipulation of vulnerable persons, predictive policing based on profiling</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>PROHIBITED — cannot be deployed in the EU.</t>
+          <t>PROHIBITED — cannot be deployed in the EU. No compliance pathway.</t>
         </is>
       </c>
     </row>
@@ -2184,85 +2211,85 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Significant impact on rights/safety.</t>
+          <t>AI systems with significant impact on fundamental rights, safety, or access to essential services.</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Employment &amp; recruitment (TalentScope AI), biometric ID, credit scoring, law enforcement, critical infrastructure</t>
+          <t>Employment &amp; recruitment (TalentScope AI falls here), biometric identification, credit scoring, law enforcement, critical infrastructure, education access, migration/asylum</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Conformity assessment, risk management, data governance, transparency, human oversight, accuracy, documentation, registration, post-market surveillance</t>
+          <t>Conformity assessment (Art 43), risk management system (Art 9), data governance (Art 10), technical documentation (Art 11), record-keeping (Art 12), transparency (Art 13), human oversight (Art 14), accuracy &amp; robustness (Art 15), registration (Art 49), post-market surveillance (Art 72)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1" s="11">
       <c r="A6" s="6" t="inlineStr">
         <is>
+          <t>GPAI / Foundation Models
+(Articles 51–55)</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>General-Purpose AI models — including those with systemic risk. Introduced by Regulation (EU) 2024/1689; obligations applicable from 2 Aug 2025.</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Providers of general-purpose foundation models — e.g. models offered via API that power customer-facing assistants, chatbots, code copilots, RAG systems.</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Provider obligations — transparency to downstream deployers (Art. 53), copyright disclosure, technical documentation; if systemic risk, additional model evaluation + adversarial testing + Art. 55 obligations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1" s="11">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
           <t>Limited Risk
 (Article 50)</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Transparency obligations.</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Chatbots, emotion recognition, deepfakes, biometric categorization</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Disclose AI usage to users.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1" s="11">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>AI systems with specific transparency obligations.</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Chatbots (must disclose AI), emotion recognition systems, deepfake generators, biometric categorization</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Must disclose to users they are interacting with AI. Limited documentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="95" customHeight="1" s="11">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Minimal Risk</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>No specific requirements.</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Spam filters, games, basic recommendations, route optimization</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Voluntary codes of conduct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="95" customHeight="1" s="11">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>GPAI / Foundation Models
-(Articles 51–55)</t>
-        </is>
-      </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>General-Purpose AI models — including those with systemic risk. Introduced by Regulation (EU) 2024/1689; obligations applicable from 2 Aug 2025.</t>
+          <t>AI systems with no specific regulatory requirements.</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Providers of general-purpose foundation models — e.g. models offered via API that power customer-facing assistants, chatbots, code copilots, RAG systems.</t>
+          <t>Spam filters, AI video games, inventory management, basic recommendation engines, route optimization</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Provider obligations — transparency to downstream deployers (Art. 53), copyright disclosure, technical documentation; if systemic risk, additional model evaluation + adversarial testing + Art. 55 obligations.</t>
+          <t>No mandatory requirements. Voluntary codes of conduct encouraged.</t>
         </is>
       </c>
     </row>

--- a/04_regulatory-compliance-for-ai-eu-ai-act/exercises/solution/compliance_plan.xlsx
+++ b/04_regulatory-compliance-for-ai-eu-ai-act/exercises/solution/compliance_plan.xlsx
@@ -881,7 +881,7 @@
       <c r="I4" s="4" t="inlineStr">
         <is>
           <t>"Complete dataset card with demographic analysis; document interview data collection, consent, and preprocessing steps"
-Reasoning: Dataset cards are industry standard for documenting training data. Demographic analysis enables the bias testing required by Article 15. Both are concrete, achievable actions.</t>
+Reasoning: Dataset cards are industry standard for documenting training data. Demographic analysis enables the bias examination required by Article 10(2)(f)-(g). Both are concrete, achievable actions.</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -1061,7 +1061,7 @@
       <c r="I7" s="4" t="inlineStr">
         <is>
           <t>"Expand bias testing to all protected characteristics (race, age, disability, accent); remediate gender disparity to &lt;2%; implement adversarial testing; establish ongoing fairness monitoring"
-Reasoning: Expanding to all protected characteristics is required by Article 15(2). The &lt;2% threshold is a concrete, measurable target. Ongoing monitoring catches new biases post-deployment.</t>
+Reasoning: Expanding to all protected characteristics is required by the bias detection and mitigation duty in Article 10(2)(f)-(g); Article 15 covers the accuracy and robustness side of this row. The &lt;2% threshold is a concrete, measurable target. Ongoing monitoring catches new biases post-deployment.</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Serious-Incident Reporting — Notify national competent authority of serious incidents per Article 73 (enforces Aug 2026)</t>
+          <t>Serious-Incident Reporting — Notify national competent authority of serious incidents per Article 73 (applies 2 Dec 2027)</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1464,7 +1464,7 @@
       <c r="F14" s="8" t="inlineStr">
         <is>
           <t>"Gap"
-Reasoning: Article 73 enforces from August 2026 for all High-Risk systems. TalentScope has no documented incident-detection-and-reporting pipeline; without it, the company will be non-compliant on day one of enforcement. Severity: high — first regulatory obligation graduates encounter at deployment.</t>
+Reasoning: Article 73 applies from 2 December 2027 for stand-alone Annex III High-Risk systems. TalentScope has no documented incident-detection-and-reporting pipeline; without it, the company will be non-compliant on day one of enforcement. Severity: high — first regulatory obligation graduates encounter at deployment.</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
@@ -1474,13 +1474,13 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>"Establish 15-day reporting SLA to national competent authority; integrate incident detection from SP6 IR playbook; assign DPO + Compliance lead as joint owners; complete documentation by Q2 2026 ahead of August 2026 enforcement."</t>
+          <t>"Establish 15-day reporting SLA to national competent authority; integrate incident detection from SP6 IR playbook; assign DPO + Compliance lead as joint owners; complete documentation ahead of the 2 December 2027 applicability date."</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>"Stand up the Article 73 reporting workflow: 15-day SLA to the national competent authority (10 days where the incident involves a person's death; 2 days for widespread infringement); wire incident detection in from the SP6 IR playbook; define the escalation path and DPO + Compliance joint sign-off; dry-run the process before Aug 2026."
-Reasoning: Article 73 becomes enforceable in August 2026, so the workflow must exist and be rehearsed before then. Reusing the SP6 detection pipeline avoids building a parallel capability, and joint DPO + Compliance sign-off matches the tiered deadlines.</t>
+          <t>"Stand up the Article 73 reporting workflow: 15-day SLA to the national competent authority (10 days where the incident involves a person's death; 2 days for widespread infringement); wire incident detection in from the SP6 IR playbook; define the escalation path and DPO + Compliance joint sign-off; dry-run the process before 2 Dec 2027."
+Reasoning: Article 73 becomes applicable on 2 December 2027, so the workflow must exist and be rehearsed before then. Reusing the SP6 detection pipeline avoids building a parallel capability, and joint DPO + Compliance sign-off matches the tiered deadlines.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>Pipeline + 15-day SLA defined; integration with SP6 IR playbook in progress; DPO + Compliance owners assigned; ready ahead of August 2026 Article 73 enforcement.</t>
+          <t>Pipeline + 15-day SLA defined; integration with SP6 IR playbook in progress; DPO + Compliance owners assigned; ready ahead of the 2 December 2027 Article 73 applicability date.</t>
         </is>
       </c>
     </row>
